--- a/data/department_schedules_finals/Çevre Mühendisliği.xlsx
+++ b/data/department_schedules_finals/Çevre Mühendisliği.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\department_schedules_finals\modified\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/department_schedules_finals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF33FDF-CB85-45B9-813E-3BECDF2DB8E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{EAF33FDF-CB85-45B9-813E-3BECDF2DB8E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{935BB47C-7E2C-42CE-8E6F-20D7937AAC38}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17640" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="64">
   <si>
     <t>Year:</t>
   </si>
@@ -194,6 +194,24 @@
   </si>
   <si>
     <t>Rooms Used</t>
+  </si>
+  <si>
+    <t>C204</t>
+  </si>
+  <si>
+    <t>CAD1</t>
+  </si>
+  <si>
+    <t>C202</t>
+  </si>
+  <si>
+    <t>Amfi 3</t>
+  </si>
+  <si>
+    <t>DZ01</t>
+  </si>
+  <si>
+    <t>YLAB 1</t>
   </si>
 </sst>
 </file>
@@ -300,6 +318,38 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -328,38 +378,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -374,15 +392,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E703AF2A-1E55-474A-BE3F-96016289569F}" name="Table1" displayName="Table1" ref="A1:F27" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="9" tableBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E703AF2A-1E55-474A-BE3F-96016289569F}" name="Table1" displayName="Table1" ref="A1:F27" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6">
   <autoFilter ref="A1:F27" xr:uid="{E703AF2A-1E55-474A-BE3F-96016289569F}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{3ECC80F5-2B5A-409B-A2FF-F6F263A9CF08}" name="Year:" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{4CC3476D-C67B-428F-9A5C-322F2371A48D}" name="Course ID" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{9E31BA35-1BAC-4638-9AAB-E2F5DECBFAA7}" name="Date" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{2346AB05-A96B-4701-BDE3-56F34456BD03}" name="Rooms" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{C1888443-E59A-4029-842A-83485EAAED9D}" name="Course Name" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{43FBA85C-D7FD-4436-A5BA-F00F9D7917BC}" name="Rooms Used" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{3ECC80F5-2B5A-409B-A2FF-F6F263A9CF08}" name="Year:" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{4CC3476D-C67B-428F-9A5C-322F2371A48D}" name="Course ID" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{9E31BA35-1BAC-4638-9AAB-E2F5DECBFAA7}" name="Date" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{2346AB05-A96B-4701-BDE3-56F34456BD03}" name="Rooms" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{C1888443-E59A-4029-842A-83485EAAED9D}" name="Course Name" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{43FBA85C-D7FD-4436-A5BA-F00F9D7917BC}" name="Rooms Used" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -676,14 +694,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="10.90625" customWidth="1"/>
-    <col min="5" max="5" width="37.08984375" customWidth="1"/>
-    <col min="6" max="6" width="50.453125" customWidth="1"/>
+    <col min="2" max="2" width="10.9296875" customWidth="1"/>
+    <col min="5" max="5" width="37.06640625" customWidth="1"/>
+    <col min="6" max="6" width="50.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -703,7 +721,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -719,9 +737,11 @@
       <c r="E2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F2" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -737,9 +757,11 @@
       <c r="E3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F3" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -755,9 +777,11 @@
       <c r="E4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F4" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -773,9 +797,11 @@
       <c r="E5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F5" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -791,9 +817,11 @@
       <c r="E6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F6" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>1</v>
       </c>
@@ -809,9 +837,11 @@
       <c r="E7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F7" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>1</v>
       </c>
@@ -827,9 +857,11 @@
       <c r="E8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F8" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>1</v>
       </c>
@@ -845,9 +877,11 @@
       <c r="E9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F9" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
         <v>2</v>
       </c>
@@ -863,9 +897,11 @@
       <c r="E10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F10" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
         <v>2</v>
       </c>
@@ -881,9 +917,11 @@
       <c r="E11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F11" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -899,9 +937,11 @@
       <c r="E12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F12" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
         <v>2</v>
       </c>
@@ -917,9 +957,11 @@
       <c r="E13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F13" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
         <v>2</v>
       </c>
@@ -935,9 +977,11 @@
       <c r="E14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F14" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
         <v>2</v>
       </c>
@@ -953,9 +997,11 @@
       <c r="E15" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F15" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
         <v>2</v>
       </c>
@@ -971,9 +1017,11 @@
       <c r="E16" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="3"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F16" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="4">
         <v>3</v>
       </c>
@@ -989,9 +1037,11 @@
       <c r="E17" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F17" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" s="4">
         <v>3</v>
       </c>
@@ -1007,9 +1057,11 @@
       <c r="E18" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F18" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" s="4">
         <v>3</v>
       </c>
@@ -1025,9 +1077,11 @@
       <c r="E19" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F19" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" s="4">
         <v>3</v>
       </c>
@@ -1043,9 +1097,11 @@
       <c r="E20" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F20" s="4"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F20" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" s="4">
         <v>3</v>
       </c>
@@ -1061,9 +1117,11 @@
       <c r="E21" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F21" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" s="4">
         <v>3</v>
       </c>
@@ -1079,9 +1137,11 @@
       <c r="E22" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F22" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" s="5">
         <v>4</v>
       </c>
@@ -1097,9 +1157,11 @@
       <c r="E23" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F23" s="5"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F23" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" s="5">
         <v>4</v>
       </c>
@@ -1115,9 +1177,11 @@
       <c r="E24" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="F24" s="5"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F24" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" s="5">
         <v>4</v>
       </c>
@@ -1133,9 +1197,11 @@
       <c r="E25" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F25" s="5"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F25" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" s="5">
         <v>4</v>
       </c>
@@ -1151,9 +1217,11 @@
       <c r="E26" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F26" s="5"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F26" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" s="5">
         <v>4</v>
       </c>
@@ -1169,7 +1237,9 @@
       <c r="E27" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F27" s="5"/>
+      <c r="F27" s="5" t="s">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
